--- a/data/trans_orig/IP1010-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198088</t>
+          <t>198037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82731</t>
+          <t>83100</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>170106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197498</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197710</t>
+          <t>197746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397968</t>
+          <t>397920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123201</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227875</t>
+          <t>227897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>71893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>68622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142279</t>
+          <t>142325</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634316</t>
+          <t>634637</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>676459</t>
+          <t>675878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>683235</t>
+          <t>683239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313811</t>
+          <t>1313685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320873</t>
+          <t>1320929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90190</t>
+          <t>90223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186606</t>
+          <t>186135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221669</t>
+          <t>222248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427448</t>
+          <t>427847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145514</t>
+          <t>145512</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135372</t>
+          <t>136347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283560</t>
+          <t>283352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>50106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123603</t>
+          <t>123578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>667917</t>
+          <t>668336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>673636</t>
+          <t>673637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>706860</t>
+          <t>707486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712816</t>
+          <t>712812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377979</t>
+          <t>1377305</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1385579</t>
+          <t>1385580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>108676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214108</t>
+          <t>213338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70952</t>
+          <t>71396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133619</t>
+          <t>132979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205743</t>
+          <t>205785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429310</t>
+          <t>428955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133557</t>
+          <t>133540</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138477</t>
+          <t>138259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274258</t>
+          <t>274044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278765</t>
+          <t>278761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>668511</t>
+          <t>668116</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>699835</t>
+          <t>700819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>708181</t>
+          <t>707739</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1371262</t>
+          <t>1371571</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1379062</t>
+          <t>1379354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1010-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1010-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>94164</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>197882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3259</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2870</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85328</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82711</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85328</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83100</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170106</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4328</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201349</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198442</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200091</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201349</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>197746</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>605</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397920</t>
+          <t>398290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126589</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124147</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126589</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123782</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4348</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71142</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>68044</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74265</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>71893</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71841</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,19%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71142</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>68622</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>216</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142325</t>
+          <t>142321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146661</t>
+          <t>146664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3991</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8965</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4219</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3991</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8725</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>680612</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>675638</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683232</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637609</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>634637</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634468</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>680612</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>675878</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683239</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1974</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313685</t>
+          <t>1313654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320929</t>
+          <t>1321454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92286</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90223</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90030</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>273</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186135</t>
+          <t>186586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,92 +4386,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4439</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1315</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4616</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>225549</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>222425</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>225549</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>222248</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427847</t>
+          <t>427846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4734,102 +4734,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5651</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4842,74 +4842,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>148273</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>145512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>144246</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136347</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>406</t>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283352</t>
+          <t>283436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5077,102 +5077,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3805</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3744</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5254</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1403</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4371</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73391</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>70789</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53155</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>50106</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>73391</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>71111</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,05%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123578</t>
+          <t>122695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5745</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>710852</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>707459</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712851</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>671986</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>668336</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>673637</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>668049</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>673636</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>710852</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>707486</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712812</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1984</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377305</t>
+          <t>1377874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1385580</t>
+          <t>1385565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,107 +6335,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4070</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5122</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111928</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108320</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111928</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108676</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213338</t>
+          <t>213524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,107 +6678,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4032</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3578</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4289</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74701</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71238</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74701</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71396</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132979</t>
+          <t>133690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1453</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5069</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5476</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>209401</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>206023</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>209401</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>205785</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428955</t>
+          <t>429357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2150</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4829</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141754</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>138504</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135670</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>133540</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>134044</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141754</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>138259</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>401</t>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274044</t>
+          <t>274071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278761</t>
+          <t>278757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4332</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8718</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3386</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8918</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>705405</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>701019</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>708216</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,79%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>670978</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>668116</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>668181</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>705405</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>700819</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>707739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2023</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1371571</t>
+          <t>1371783</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1379354</t>
+          <t>1379191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
